--- a/Results/TestCases/XLSX/time_TestCases.xlsx
+++ b/Results/TestCases/XLSX/time_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="71">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -72,13 +72,16 @@
     <t>High</t>
   </si>
   <si>
-    <t>SKIPPED</t>
+    <t>PASSED</t>
   </si>
   <si>
     <t>TC_TIME_02</t>
   </si>
   <si>
     <t>Verify access to My Timesheets page</t>
+  </si>
+  <si>
+    <t>FAILED</t>
   </si>
   <si>
     <t>TC_TIME_03</t>
@@ -229,7 +232,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -249,12 +252,18 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF5A6268"/>
+      <color rgb="FF107C41"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFA51D24"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -268,7 +277,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E3E5"/>
+        <fgColor rgb="FFD1E7DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -310,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -319,6 +333,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -774,13 +791,13 @@
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>19</v>
+      <c r="K3" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -789,13 +806,13 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -809,13 +826,13 @@
       <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>19</v>
+      <c r="K4" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -824,14 +841,14 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
       </c>
@@ -842,15 +859,15 @@
         <v>17</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -859,13 +876,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -877,7 +894,7 @@
         <v>17</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>19</v>
@@ -885,7 +902,7 @@
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -894,13 +911,13 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -912,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>19</v>
@@ -920,7 +937,7 @@
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -929,13 +946,13 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -947,7 +964,7 @@
         <v>17</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>19</v>
@@ -955,7 +972,7 @@
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -964,13 +981,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -982,15 +999,15 @@
         <v>17</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -999,13 +1016,13 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -1017,15 +1034,15 @@
         <v>17</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1034,13 +1051,13 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -1052,15 +1069,15 @@
         <v>17</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1069,13 +1086,13 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -1087,15 +1104,15 @@
         <v>17</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1104,13 +1121,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -1122,7 +1139,7 @@
         <v>17</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>19</v>
@@ -1130,7 +1147,7 @@
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1139,13 +1156,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -1157,15 +1174,15 @@
         <v>17</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1174,13 +1191,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -1192,15 +1209,15 @@
         <v>17</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1209,13 +1226,13 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -1227,15 +1244,15 @@
         <v>17</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1244,13 +1261,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -1262,15 +1279,15 @@
         <v>17</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1279,13 +1296,13 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -1297,15 +1314,15 @@
         <v>17</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1314,13 +1331,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -1332,15 +1349,15 @@
         <v>17</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1349,13 +1366,13 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -1367,15 +1384,15 @@
         <v>17</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1384,13 +1401,13 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -1402,15 +1419,15 @@
         <v>17</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1419,13 +1436,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1437,15 +1454,15 @@
         <v>17</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1454,13 +1471,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1472,7 +1489,7 @@
         <v>17</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>19</v>
@@ -1480,7 +1497,7 @@
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1489,13 +1506,13 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -1507,7 +1524,7 @@
         <v>17</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>19</v>
@@ -1515,7 +1532,7 @@
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1524,13 +1541,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1542,7 +1559,7 @@
         <v>17</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>19</v>
@@ -1550,7 +1567,7 @@
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1559,13 +1576,13 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -1577,10 +1594,10 @@
         <v>17</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Results/TestCases/XLSX/time_TestCases.xlsx
+++ b/Results/TestCases/XLSX/time_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="111">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -58,15 +58,14 @@
     <t>Positive</t>
   </si>
   <si>
-    <t>OrangeHRM application is accessible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to page
-2. Perform test actions
-3. Verify assertions</t>
-  </si>
-  <si>
-    <t>Test executes successfully and all assertions pass</t>
+    <t>The user is logged in to OrangeHRM with valid credentials and the Dashboard has loaded. The user has navigated to the 'Time' module.</t>
+  </si>
+  <si>
+    <t>1. Perform the actions described in the test title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The header should equal 'Time'
+- The tabs visible should equal 'true'</t>
   </si>
   <si>
     <t>High</t>
@@ -81,121 +80,210 @@
     <t>Verify access to My Timesheets page</t>
   </si>
   <si>
+    <t>1. Navigate to the My Timesheets page</t>
+  </si>
+  <si>
+    <t>- The heading should be visible</t>
+  </si>
+  <si>
+    <t>TC_TIME_03</t>
+  </si>
+  <si>
+    <t>Verify access to Punch In/Out attendance page</t>
+  </si>
+  <si>
+    <t>1. Navigate to the Punch In/Out page</t>
+  </si>
+  <si>
+    <t>- The 'Punch In' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_TIME_04</t>
+  </si>
+  <si>
+    <t>Verify search button validation with empty/invalid inputs in employee timesheets</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click the Timesheets tab
+2. Click the Employee Timesheets link
+3. Click the View button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The error text should be visible
+- The error text should display the text 'Required'</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>TC_TIME_05</t>
+  </si>
+  <si>
+    <t>Verify top navigation contains Reports tab</t>
+  </si>
+  <si>
+    <t>- The Reports tab should be visible</t>
+  </si>
+  <si>
+    <t>TC_TIME_06</t>
+  </si>
+  <si>
+    <t>Verify top navigation contains Project Info tab</t>
+  </si>
+  <si>
+    <t>- The Project Info tab should be visible</t>
+  </si>
+  <si>
+    <t>TC_TIME_07</t>
+  </si>
+  <si>
+    <t>Verify Customers option exists under Project Info</t>
+  </si>
+  <si>
+    <t>1. Click the Project Info tab</t>
+  </si>
+  <si>
+    <t>- The 'Customers' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_TIME_08</t>
+  </si>
+  <si>
+    <t>Verify Projects option exists under Project Info</t>
+  </si>
+  <si>
+    <t>- The 'Projects' element should be visible</t>
+  </si>
+  <si>
+    <t>TC_TIME_09</t>
+  </si>
+  <si>
+    <t>Verify Project Info menu contains exactly Customers and Projects options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The items should have a count of '2'
+- The items.nth(0) should display the text 'Customers'
+- The items.nth(1) should display the text 'Projects'</t>
+  </si>
+  <si>
     <t>FAILED</t>
   </si>
   <si>
-    <t>TC_TIME_03</t>
-  </si>
-  <si>
-    <t>Verify access to Punch In/Out attendance page</t>
-  </si>
-  <si>
-    <t>TC_TIME_04</t>
-  </si>
-  <si>
-    <t>Verify search button validation with empty/invalid inputs in employee timesheets</t>
-  </si>
-  <si>
-    <t>Negative</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>TC_TIME_05</t>
-  </si>
-  <si>
-    <t>Verify top navigation contains Reports tab</t>
-  </si>
-  <si>
-    <t>TC_TIME_06</t>
-  </si>
-  <si>
-    <t>Verify top navigation contains Project Info tab</t>
-  </si>
-  <si>
-    <t>TC_TIME_07</t>
-  </si>
-  <si>
-    <t>Verify Customers option exists under Project Info</t>
-  </si>
-  <si>
-    <t>TC_TIME_08</t>
-  </si>
-  <si>
-    <t>Verify Projects option exists under Project Info</t>
-  </si>
-  <si>
-    <t>TC_TIME_09</t>
-  </si>
-  <si>
-    <t>Verify Activities option exists under Project Info</t>
-  </si>
-  <si>
     <t>TC_TIME_10</t>
   </si>
   <si>
     <t>Verify Project Reports option exists under Reports menu</t>
   </si>
   <si>
+    <t>1. Click the Reports tab</t>
+  </si>
+  <si>
+    <t>- The 'Project Reports' element should be visible</t>
+  </si>
+  <si>
     <t>TC_TIME_11</t>
   </si>
   <si>
     <t>Verify Employee Reports option exists under Reports menu</t>
   </si>
   <si>
+    <t>- The 'Employee Reports' element should be visible</t>
+  </si>
+  <si>
     <t>TC_TIME_12</t>
   </si>
   <si>
     <t>Verify Attendance Summary option exists under Reports menu</t>
   </si>
   <si>
+    <t>- The 'Attendance Summary' element should be visible</t>
+  </si>
+  <si>
     <t>TC_TIME_13</t>
   </si>
   <si>
     <t>Verify employee name search input field exists on Employee Timesheets page</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the Timesheets tab
+2. Click the Employee Timesheets link</t>
+  </si>
+  <si>
+    <t>- The Employee Name field should be visible</t>
+  </si>
+  <si>
     <t>TC_TIME_14</t>
   </si>
   <si>
     <t>Verify punch page has date input element</t>
   </si>
   <si>
+    <t>- The date input should be visible</t>
+  </si>
+  <si>
     <t>TC_TIME_15</t>
   </si>
   <si>
     <t>Verify punch page has time input element</t>
   </si>
   <si>
+    <t>- The time input should be visible</t>
+  </si>
+  <si>
     <t>TC_TIME_16</t>
   </si>
   <si>
     <t>Verify punch page note textarea is functional</t>
   </si>
   <si>
+    <t>- The textarea element should be visible</t>
+  </si>
+  <si>
     <t>TC_TIME_17</t>
   </si>
   <si>
     <t>Verify attendance table headers in My Records page</t>
   </si>
   <si>
+    <t>1. Navigate to the Attendance My Records page</t>
+  </si>
+  <si>
+    <t>- The col header should be visible</t>
+  </si>
+  <si>
     <t>TC_TIME_18</t>
   </si>
   <si>
     <t>Verify My Records date picker input elements exist</t>
   </si>
   <si>
+    <t>- The await date inputs.count() should be greater than '0'</t>
+  </si>
+  <si>
     <t>TC_TIME_19</t>
   </si>
   <si>
     <t>Verify calendar pop-up opens on clicking date input in My Records page</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Navigate to the Attendance My Records page
+2. Click the date input</t>
+  </si>
+  <si>
+    <t>- The calendar should be visible</t>
+  </si>
+  <si>
     <t>TC_TIME_20</t>
   </si>
   <si>
-    <t>Verify Reset button clears search filters in My Records page</t>
+    <t>Verify Date filter and View button are present in My Records page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The date input should be visible
+- The 'View' element should be visible</t>
   </si>
   <si>
     <t>TC_TIME_21</t>
@@ -204,28 +292,70 @@
     <t>Verify view records button text contains View</t>
   </si>
   <si>
+    <t>- The submit element should display the text 'View'</t>
+  </si>
+  <si>
     <t>TC_TIME_22</t>
   </si>
   <si>
     <t>Verify breadcrumb title text details are visible</t>
   </si>
   <si>
+    <t>- The breadcrumb should contain the text 'Time'</t>
+  </si>
+  <si>
     <t>TC_TIME_23</t>
   </si>
   <si>
     <t>Verify Timesheets menu is visible in sub-navigation bar</t>
   </si>
   <si>
+    <t>- The Timesheets tab should be visible</t>
+  </si>
+  <si>
     <t>TC_TIME_24</t>
   </si>
   <si>
     <t>Verify Attendance menu is visible in sub-navigation bar</t>
   </si>
   <si>
+    <t>- The Attendance tab should be visible</t>
+  </si>
+  <si>
     <t>TC_TIME_25</t>
   </si>
   <si>
     <t>Verify Punch In button exists in Punch page when logged out or punched out</t>
+  </si>
+  <si>
+    <t>- The await in btn.count() should be greater than '0'</t>
+  </si>
+  <si>
+    <t>TC_TIME_26</t>
+  </si>
+  <si>
+    <t>Verify Employee Records option is visible under Attendance menu</t>
+  </si>
+  <si>
+    <t>1. Click the Attendance tab</t>
+  </si>
+  <si>
+    <t>- The Employee Records link should be visible</t>
+  </si>
+  <si>
+    <t>TC_TIME_27</t>
+  </si>
+  <si>
+    <t>Verify Employee Timesheets search with a non-existent employee name shows required validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click the Timesheets tab
+2. Click the Employee Timesheets link
+3. Enter 'NonExistentEmployeeXYZ' into the Employee Name field
+4. Click the View button</t>
+  </si>
+  <si>
+    <t>- The error text should be visible</t>
   </si>
 </sst>
 </file>
@@ -677,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -783,21 +913,21 @@
         <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>22</v>
+      <c r="K3" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -806,33 +936,33 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>22</v>
+      <c r="K4" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -841,33 +971,33 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -876,13 +1006,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -891,10 +1021,10 @@
         <v>16</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>19</v>
@@ -902,7 +1032,7 @@
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -911,13 +1041,13 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -926,10 +1056,10 @@
         <v>16</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>19</v>
@@ -937,7 +1067,7 @@
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -946,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>19</v>
@@ -972,7 +1102,7 @@
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -981,33 +1111,33 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -1016,33 +1146,33 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1051,33 +1181,33 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1086,33 +1216,33 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1121,25 +1251,25 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>19</v>
@@ -1147,7 +1277,7 @@
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1156,33 +1286,33 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1191,33 +1321,33 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1226,33 +1356,33 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1261,33 +1391,33 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1296,33 +1426,33 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1331,33 +1461,33 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1366,33 +1496,33 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1401,33 +1531,33 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1436,33 +1566,33 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1471,13 +1601,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1486,10 +1616,10 @@
         <v>16</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>19</v>
@@ -1497,7 +1627,7 @@
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1506,13 +1636,13 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -1521,10 +1651,10 @@
         <v>16</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>19</v>
@@ -1532,7 +1662,7 @@
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1541,13 +1671,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1556,10 +1686,10 @@
         <v>16</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>19</v>
@@ -1567,7 +1697,7 @@
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1576,28 +1706,98 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>22</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Results/TestCases/XLSX/time_TestCases.xlsx
+++ b/Results/TestCases/XLSX/time_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="110">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -167,9 +167,6 @@
     <t xml:space="preserve">- The items should have a count of '2'
 - The items.nth(0) should display the text 'Customers'
 - The items.nth(1) should display the text 'Projects'</t>
-  </si>
-  <si>
-    <t>FAILED</t>
   </si>
   <si>
     <t>TC_TIME_10</t>
@@ -362,7 +359,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -386,14 +383,8 @@
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="FFA51D24"/>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -408,11 +399,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD1E7DD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -454,7 +440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -463,9 +449,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1166,37 +1149,37 @@
       <c r="J10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K10" s="4" t="s">
-        <v>50</v>
+      <c r="K10" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>33</v>
@@ -1207,31 +1190,31 @@
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>33</v>
@@ -1242,31 +1225,31 @@
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>33</v>
@@ -1277,31 +1260,31 @@
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>33</v>
@@ -1312,22 +1295,22 @@
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -1336,7 +1319,7 @@
         <v>26</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>33</v>
@@ -1347,22 +1330,22 @@
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -1371,7 +1354,7 @@
         <v>26</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>33</v>
@@ -1382,22 +1365,22 @@
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -1406,7 +1389,7 @@
         <v>26</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>33</v>
@@ -1417,31 +1400,31 @@
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>33</v>
@@ -1452,66 +1435,66 @@
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="J19" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K19" s="4" t="s">
-        <v>50</v>
+      <c r="K19" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="2" t="s">
+      <c r="I20" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>33</v>
@@ -1522,66 +1505,66 @@
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="J21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K21" s="4" t="s">
-        <v>50</v>
+      <c r="K21" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>33</v>
@@ -1592,22 +1575,22 @@
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1616,7 +1599,7 @@
         <v>16</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>33</v>
@@ -1627,22 +1610,22 @@
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -1651,7 +1634,7 @@
         <v>16</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>33</v>
@@ -1662,22 +1645,22 @@
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1686,7 +1669,7 @@
         <v>16</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>33</v>
@@ -1697,22 +1680,22 @@
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -1721,42 +1704,42 @@
         <v>26</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K26" s="4" t="s">
-        <v>50</v>
+      <c r="K26" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="27" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H27" s="2" t="s">
+      <c r="I27" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>33</v>
@@ -1767,31 +1750,31 @@
     </row>
     <row r="28" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H28" s="2" t="s">
+      <c r="I28" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>33</v>
